--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
@@ -702,7 +702,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall place base_link above base_footprint by wheel_radius minus the wheel axis height above body_link (0.033 m), with base_link coincident with body_link.</t>
+          <t>The rover_description shall place base_link above base_footprint by tyre_radius minus the wheel axis height above body_link (0.037363 m), with base_link coincident with body_link.</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>footprint_to_base_joint z equals wheel_radius - 0.033 = 0.1321 m with wheel_01.yaml; base_to_body_joint origin is (0, 0, 0).</t>
+          <t>footprint_to_base_joint z equals tyre_radius - 0.037363 = 0.132537 m with wheel_01.yaml; base_to_body_joint origin is (0, 0, 0).</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>rover_description/urdf/rover_a1/rover_a1_macro.urdf.xacro:37-38; rover_description/urdf/rover_a1/base.urdf.xacro:20-33</t>
+          <t>rover_description/urdf/rover_a1/rover_a1_macro.urdf.xacro:41-43; rover_description/urdf/rover_a1/rover_a1_macro.urdf.xacro:66-67; rover_description/urdf/rover_a1/base.urdf.xacro:20-33</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
@@ -751,7 +751,11 @@
         </is>
       </c>
       <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Axis height from the SolidWorks export (joint_*_* origin z in rover_description/solidworks_exported/ROVER_1000_WATT_VARIANT.SLDASM/urdf/*.csv, re-exported 2026-10-07).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -766,7 +770,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall take wheel geometry only from config/wheel_01.yaml (wheel_radius 0.1651 m, wheel_width 0.108 m, wheelbase 0.503 m, wheel_separation 0.615 m) and mount the fl, fr, rl and rr wheels at (+/-wheelbase/2, +/-wheel_separation/2) in their REP-103 quadrants at a common height.</t>
+          <t>The rover_description shall take wheel geometry only from config/wheel_01.yaml (tyre_radius 0.1699 m, wheel_width 0.108 m, wheelbase 0.503 m, wheel_separation 0.617 m, tyre_y_offset -0.00171 m) and mount the fl, fr, rl and rr wheels at (+/-wheelbase/2, +/-wheel_separation/2) in their REP-103 quadrants at a common height, with each tyre collision cylinder |tyre_y_offset| inboard of its joint.</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -781,7 +785,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>For each prefix the body_to_&lt;prefix&gt;_wheel_base_joint origin equals (sx*0.2515, sy*0.3075, 0.033) with the quadrant signs fl(+,+), fr(+,-), rl(-,+), rr(-,-).</t>
+          <t>For each prefix the body_to_&lt;prefix&gt;_wheel_base_joint origin equals (sx*0.2515, sy*0.3085, 0.037363) with the quadrant signs fl(+,+), fr(+,-), rl(-,+), rr(-,-), and the &lt;prefix&gt;_wheel_link collision origin y equals -sy*0.00171 (contact patches 0.6136 m apart).</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -801,7 +805,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>rover_description/config/wheel_01.yaml:1-10; rover_description/urdf/rover_a1/rover_a1_macro.urdf.xacro:32-36; rover_description/urdf/rover_a1/rover_a1_macro.urdf.xacro:71-101; rover_description/urdf/common/wheel.urdf.xacro:7-37</t>
+          <t>rover_description/config/wheel_01.yaml:1-22; rover_description/urdf/rover_a1/rover_a1_macro.urdf.xacro:37-43; rover_description/urdf/rover_a1/rover_a1_macro.urdf.xacro:79-108; rover_description/urdf/common/wheel.urdf.xacro:7-41; rover_description/urdf/common/wheel.urdf.xacro:67-72</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -815,7 +819,11 @@
         </is>
       </c>
       <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Values from the SolidWorks export of 2026-10-07: wheel joints at x +0.2515 / -0.25156, y +/-0.30851, z 0.037363; tread band of link_*.STL centred 1.71 mm inboard of the joint.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1286,7 +1294,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare body_link inertial mass 33.445952 kg and each wheel link mass 2.5 kg (43.445952 kg in total).</t>
+          <t>The rover_description shall declare body_link inertial mass 36.9775 kg and each wheel link mass 5.0741 kg (57.2739 kg in total).</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1301,7 +1309,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Sum of all &lt;mass&gt; values in the generated URDF equals 43.445952 kg; a physical weighing of the assembled platform is &lt;= 60.0 kg (SYS-SR-001).</t>
+          <t>Sum of all &lt;mass&gt; values in the generated URDF equals 57.2739 kg; a physical weighing of the assembled platform is &lt;= 60.0 kg (SYS-SR-001).</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1321,7 +1329,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>rover_description/urdf/rover_a1/base.urdf.xacro:54-59; rover_description/config/wheel_01.yaml:3; rover_description/urdf/common/wheel.urdf.xacro:70-80</t>
+          <t>rover_description/urdf/rover_a1/base.urdf.xacro:68-79; rover_description/config/wheel_01.yaml:10; rover_description/urdf/common/wheel.urdf.xacro:74-84</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1333,7 +1341,7 @@
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Mass fidelity: the modelled 43.45 kg is a CAD body + nominal wheels and is not a measured value; it does not by itself verify SYS-SR-001. The survey reported a higher CAD total mass on the SYS-SR-001 source sheet (not present in the repository, TBC). Sensors and battery have no inertial links.</t>
+          <t>Mass fidelity: 57.27 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, re-exported 2026-10-07, batteries included), not a measured value; it does not by itself verify SYS-SR-001. The four DCC1000 motor controllers carry an ASSUMPTION mass (78.8 g each, not weighed). The URDF exporter ignores mass overrides, so body_link mass is the exported 37.2298 kg corrected by -0.2522 kg by hand (base.urdf.xacro comment). Sensors have no inertial links.</t>
         </is>
       </c>
     </row>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare body_link inertial mass 36.9775 kg and each wheel link mass 5.0741 kg (57.2739 kg in total).</t>
+          <t>The rover_description shall declare body_link inertial mass 39.5373 kg and each wheel link mass 4.79607 kg (58.7216 kg in total).</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Sum of all &lt;mass&gt; values in the generated URDF equals 57.2739 kg; a physical weighing of the assembled platform is &lt;= 60.0 kg (SYS-SR-001).</t>
+          <t>Sum of all &lt;mass&gt; values in the generated URDF equals 58.7216 kg; a physical weighing of the assembled platform is &lt;= 60.0 kg (SYS-SR-001).</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>rover_description/urdf/rover_a1/base.urdf.xacro:68-79; rover_description/config/wheel_01.yaml:10; rover_description/urdf/common/wheel.urdf.xacro:74-84</t>
+          <t>rover_description/urdf/rover_a1/base.urdf.xacro:68-81; rover_description/config/wheel_01.yaml:10-14; rover_description/urdf/common/wheel.urdf.xacro:74-84</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
@@ -1341,7 +1341,7 @@
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Mass fidelity: 57.27 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, re-exported 2026-10-07, batteries included), not a measured value; it does not by itself verify SYS-SR-001. The four DCC1000 motor controllers carry an ASSUMPTION mass (78.8 g each, not weighed). The URDF exporter ignores mass overrides, so body_link mass is the exported 37.2298 kg corrected by -0.2522 kg by hand (base.urdf.xacro comment). Sensors have no inertial links.</t>
+          <t>Mass fidelity: 58.72 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, 2026-10-08, batteries included), not a measured value; it does not by itself verify SYS-SR-001. Body and wheel inertials are computed from the per-part SolidWorks mass properties, which honour the mass overrides that the URDF exporter ignores: DCC1000 78.8 g each (ASSUMPTION, not weighed), RUTX11 456 g (distributor spec), LiFePO4 battery 5 kg (owner value). The exporter's body inertia (izz 0.57 kg m^2) does not add up to the assembly yaw inertia (6.19 kg m^2) and is not used. Sensors have no inertial links.</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
@@ -1294,7 +1294,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare body_link inertial mass 39.5373 kg and each wheel link mass 4.79607 kg (58.7216 kg in total).</t>
+          <t>The rover_description shall declare body_link inertial mass 39.5026 kg and each wheel link mass 4.79294 kg (58.6744 kg in total).</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>Sum of all &lt;mass&gt; values in the generated URDF equals 58.7216 kg; a physical weighing of the assembled platform is &lt;= 60.0 kg (SYS-SR-001).</t>
+          <t>Sum of all &lt;mass&gt; values in the generated URDF equals 58.6744 kg; a physical weighing of the assembled platform is &lt;= 60.0 kg (SYS-SR-001).</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1341,7 +1341,7 @@
       <c r="M13" s="3" t="n"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>Mass fidelity: 58.72 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, 2026-10-08, batteries included), not a measured value; it does not by itself verify SYS-SR-001. Body and wheel inertials are computed from the per-part SolidWorks mass properties, which honour the mass overrides that the URDF exporter ignores: DCC1000 78.8 g each (ASSUMPTION, not weighed), RUTX11 456 g (distributor spec), LiFePO4 battery 5 kg (owner value). The exporter's body inertia (izz 0.57 kg m^2) does not add up to the assembly yaw inertia (6.19 kg m^2) and is not used. Sensors have no inertial links.</t>
+          <t>Mass fidelity: 58.67 kg is the SolidWorks assembly mass (ROVER_1000_WATT_VARIANT, 2026-10-08 after the clash fixes, batteries included), not a measured value; it does not by itself verify SYS-SR-001. Body and wheel inertials are computed from the per-part SolidWorks mass properties, which honour the mass overrides that the URDF exporter ignores: DCC1000 78.8 g each (ASSUMPTION, not weighed), RUTX11 456 g (distributor spec), LiFePO4 battery 5 kg (owner value). The exporter's body inertia (izz 0.57 kg m^2) does not add up to the assembly yaw inertia (6.18 kg m^2) and is not used. Sensors have no inertial links.</t>
         </is>
       </c>
     </row>

--- a/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
+++ b/rover_platform_mbse/export/ROVER-A1-ROVER_DESCRIPTION-SWRS-V-001.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare, with use_sim false, a &lt;ros2_control&gt; system component named "&lt;namespace&gt;/rover_system_node" using plugin rover_hardware_interface/RoverA1System with the four wheel joints each exposing a velocity command interface and position, velocity and effort state interfaces, and with use_sim true the plugin gz_ros2_control/GazeboSimSystem with the same joints plus the IMU state interfaces.</t>
+          <t>The rover_description shall declare, with use_sim false, a &lt;ros2_control&gt; system component named "rover_system_node" (no namespace prefix: its node is rover_system_node in the controller manager's namespace, e.g. /rover/rover_system_node) using plugin rover_hardware_interface/RoverA1System with the four wheel joints each exposing a velocity command interface and position, velocity and effort state interfaces, and with use_sim true the plugin gz_ros2_control/GazeboSimSystem with the same joints plus the IMU state interfaces.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall declare, with use_sim false, a &lt;ros2_control&gt; sensor component "&lt;namespace&gt;/rover_imu" using plugin rover_hardware_interface/PhidgetImuSensor with data_interval_ms 8, callback_delta_epsilon_ms 1, Madgwick gain 0.00304 and zeta 0.00151, use_mag false, stateless false, remove_gravity_vector false and world_frame enu, exporting the 10 orientation / angular_velocity / linear_acceleration state interfaces.</t>
+          <t>The rover_description shall declare, with use_sim false, a &lt;ros2_control&gt; sensor component "rover_imu" (no namespace prefix: its node is rover_imu in the controller manager's namespace, e.g. /rover/rover_imu) using plugin rover_hardware_interface/PhidgetImuSensor with data_interval_ms 8, callback_delta_epsilon_ms 1, Madgwick gain 0.00304 and zeta 0.00151, use_mag false, stateless false, remove_gravity_vector false and world_frame enu, exporting the 10 orientation / angular_velocity / linear_acceleration state interfaces.</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>The rover_description shall, in rover_load_urdf.launch.py, take the IMU, lidar and GPS mount poses from the ROVER_{IMU,LIDAR,GPS}_LOCALIZATION_{X,Y,Z} and _ORIENTATION_{R,P,Y} environment variables, falling back to the defaults (IMU xyz (-0.09, 0.0, 0.2), rpy (3.14159, 0.0, 0.0); lidar and GPS all 0.0) for unset or non-finite values.</t>
+          <t>The rover_description shall, in rover_load_urdf.launch.py, take the IMU, lidar and GPS mount poses from the ROVER_SYSTEM_MOUNT_{IMU,LIDAR,GPS}_{X,Y,Z} and _{ROLL,PITCH,YAW} environment variables, falling back to the defaults (IMU xyz (-0.09, 0.0, 0.2), rpy (3.14159, 0.0, 0.0); lidar and GPS all 0.0) for unset or non-finite values.</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -1786,7 +1786,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
